--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -803,8 +803,8 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="34105-7"/&gt;
-    &lt;display value="Hospital Discharge summary"/&gt;
+    &lt;code value="18842-5"/&gt;
+    &lt;display value="Discharge summary"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1719,7 +1719,7 @@
     <t>Composition.section:hospitalCourse.title</t>
   </si>
   <si>
-    <t>Hospital Course</t>
+    <t>Course of Encounter</t>
   </si>
   <si>
     <t>Composition.section:hospitalCourse.code</t>
@@ -1729,7 +1729,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="8648-8"/&gt;
-    &lt;display value="Hospital course note"/&gt;
+    &lt;display value="Course of Encounter"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/resq-stroke-discharge-composition</t>
+    <t>http://qualityregistry.org/StructureDefinition/resq-stroke-discharge-composition</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -809,7 +809,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/resq-stroke-discharge-document-type-vs</t>
+    <t>http://qualityregistry.org/ValueSet/resq-stroke-discharge-document-type-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1387,7 +1387,7 @@
     <t>Provides computable standardized labels to topics within the document.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/resq-stroke-discharge-section-code-vs</t>
+    <t>http://qualityregistry.org/ValueSet/resq-stroke-discharge-section-code-vs</t>
   </si>
   <si>
     <t>Composition.section.author</t>
@@ -2625,7 +2625,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.39453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1719,7 +1719,7 @@
     <t>Composition.section:hospitalCourse.title</t>
   </si>
   <si>
-    <t>Course of Encounter</t>
+    <t>Hospital Course</t>
   </si>
   <si>
     <t>Composition.section:hospitalCourse.code</t>
@@ -1729,7 +1729,7 @@
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
     &lt;code value="8648-8"/&gt;
-    &lt;display value="Course of Encounter"/&gt;
+    &lt;display value="Hospital course note"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-resq-stroke-discharge-composition.xlsx
+++ b/StructureDefinition-resq-stroke-discharge-composition.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
